--- a/data/trans_orig/IP07KS_C02_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C02_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse lleno/a de energía en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse lleno/a de energía, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20678</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14239</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25378</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19892</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15976</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24348</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>41406</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>34372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46983</t>
+          <t>48102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16425</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11501</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22598</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8596</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4624</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12965</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15908</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20859</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>18787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5864</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,7%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5332</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5721</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1168</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5923</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5370</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1168</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5512</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19132</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13766</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24366</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>57,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19037</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14467</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23123</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>15343</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23643</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37807</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30881</t>
+          <t>31293</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44301</t>
+          <t>46243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14063</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8829</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19429</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>58,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11623</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7040</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15659</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10095</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20216</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,05%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9582</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6554</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12484</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>65,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>85,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21317</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>19623</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32197</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9714</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5256</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,36%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4571</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7740</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>31,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19719</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>354</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>956</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -2423,107 +2423,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>999</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4545</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5494</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5128</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5443</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>42043</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30240</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>50583</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>60,57%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>72,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>47648</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>32260</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>59848</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>70,95%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48,04%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42544</t>
+          <t>24002</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>90192</t>
+          <t>66046</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70892</t>
+          <t>52639</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112961</t>
+          <t>76892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>19322</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12031</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>30966</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>27,84%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>17,33%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>44,61%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>18284</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>6362</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>33114</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>24168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>37613</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>28092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>53221</t>
+          <t>49683</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>20937</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>30,16%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2809</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>7022</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>23208</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>21188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6118</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4050</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3458</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6570</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>39650</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>31177</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>48765</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>67,04%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>52,71%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>18399</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>13402</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>23405</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>51,52%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>37,53%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>65,54%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33611</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51194</t>
+          <t>25152</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>60101</t>
+          <t>59465</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50101</t>
+          <t>49775</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>72676</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13703</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6719</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>21345</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>36,09%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>11725</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>7533</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>17028</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>32,84%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>47,68%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>24968</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4614</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1544</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>9667</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>4833</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2266</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>9257</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>16742</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>876</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>891</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>20384</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24140</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22961</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27938</t>
+          <t>26719</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>43344</t>
+          <t>45759</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>38056</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>50142</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>74,86%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10866</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>6207</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>17102</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>17,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>46,83%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>9793</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>6037</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>14401</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>47,72%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>20402</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -4356,107 +4356,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>5096</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>13,95%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>1636</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>5129</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>1634</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>1636</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>5759</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -4582,107 +4582,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>897</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>4274</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>4393</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>4474</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>4208</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>160285</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>143244</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>177926</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>60,46%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>54,03%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>67,11%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>134941</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>118048</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>161075</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>56,96%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,72%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>162916</t>
+          <t>117578</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>145789</t>
+          <t>104160</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>180932</t>
+          <t>129188</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>297857</t>
+          <t>277864</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>274128</t>
+          <t>256569</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>332712</t>
+          <t>298773</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>65,06%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>84095</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>68760</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>101962</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>31,72%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>25,93%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>38,46%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>60488</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>40435</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>75668</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>82110</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>67063</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>76704</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>142599</t>
+          <t>147365</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>112430</t>
+          <t>127251</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>164114</t>
+          <t>167892</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>14606</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>7387</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>28376</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>10384</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>5566</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>17638</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>39348</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>17155</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>45163</t>
+          <t>40568</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>8570</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>3031</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>8678</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>4574</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>880</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>7893</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
